--- a/data/trans_orig/IP18_E_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP18_E_R-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>75118</t>
+          <t>75420</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>85772</t>
+          <t>85828</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>61625</t>
+          <t>61394</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>72460</t>
+          <t>72786</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>141016</t>
+          <t>140943</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>156603</t>
+          <t>156485</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,36%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8042</t>
+          <t>7986</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18696</t>
+          <t>18394</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10835</t>
+          <t>10509</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21670</t>
+          <t>21901</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20506</t>
+          <t>20624</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36093</t>
+          <t>36166</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,42%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64917</t>
+          <t>65767</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73916</t>
+          <t>74364</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62183</t>
+          <t>61890</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69842</t>
+          <t>69370</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>130685</t>
+          <t>130254</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>141815</t>
+          <t>141508</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,35%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5067</t>
+          <t>4619</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14066</t>
+          <t>13216</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2759</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10418</t>
+          <t>10711</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9769</t>
+          <t>10076</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>20899</t>
+          <t>21330</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,07%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53393</t>
+          <t>53061</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58835</t>
+          <t>58830</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75136</t>
+          <t>75045</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82550</t>
+          <t>82532</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>131062</t>
+          <t>131700</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>140491</t>
+          <t>140503</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,44%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>542</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5979</t>
+          <t>6311</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2272</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9686</t>
+          <t>9777</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3704</t>
+          <t>3692</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13133</t>
+          <t>12495</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>152889</t>
+          <t>152770</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>162652</t>
+          <t>162324</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>160973</t>
+          <t>161258</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>169931</t>
+          <t>169907</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>318102</t>
+          <t>317658</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>330742</t>
+          <t>330692</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,69%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5368</t>
+          <t>5696</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15131</t>
+          <t>15250</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13008</t>
+          <t>12723</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11259</t>
+          <t>11309</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23899</t>
+          <t>24343</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>82177</t>
+          <t>82135</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>96078</t>
+          <t>96338</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>180812</t>
+          <t>180761</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>186492</t>
+          <t>186593</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3703</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5365</t>
+          <t>5105</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>689</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6470</t>
+          <t>6521</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>61348</t>
+          <t>60765</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>66984</t>
+          <t>66895</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>57902</t>
+          <t>58115</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>64929</t>
+          <t>64838</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>121570</t>
+          <t>121747</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>131034</t>
+          <t>130576</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,05%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6824</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1448</t>
+          <t>1539</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8475</t>
+          <t>8262</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3515</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12979</t>
+          <t>12802</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>506003</t>
+          <t>506830</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>525139</t>
+          <t>525397</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>531562</t>
+          <t>531108</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>551516</t>
+          <t>550620</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1045354</t>
+          <t>1044540</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1072251</t>
+          <t>1071758</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,29%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>29061</t>
+          <t>28803</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>48197</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>31003</t>
+          <t>31899</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>50957</t>
+          <t>51411</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>64468</t>
+          <t>64961</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>91365</t>
+          <t>92179</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>68619</t>
+          <t>68742</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>77731</t>
+          <t>77893</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>69066</t>
+          <t>68205</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>79355</t>
+          <t>79301</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>141678</t>
+          <t>141193</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>155375</t>
+          <t>155162</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,75%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4865</t>
+          <t>4703</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13977</t>
+          <t>13854</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7173</t>
+          <t>7227</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17462</t>
+          <t>18323</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13748</t>
+          <t>13961</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27445</t>
+          <t>27930</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,51%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70616</t>
+          <t>69917</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>80964</t>
+          <t>80979</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>75218</t>
+          <t>74871</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>84221</t>
+          <t>84100</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>149720</t>
+          <t>149518</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>163898</t>
+          <t>163640</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,49%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7505</t>
+          <t>7490</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17853</t>
+          <t>18552</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4238</t>
+          <t>4359</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13241</t>
+          <t>13588</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13030</t>
+          <t>13288</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>27208</t>
+          <t>27410</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,49%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>75423</t>
+          <t>75099</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81683</t>
+          <t>81454</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>77164</t>
+          <t>77816</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82941</t>
+          <t>82942</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>156580</t>
+          <t>156484</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>163920</t>
+          <t>163962</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>913</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6944</t>
+          <t>7268</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>672</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6450</t>
+          <t>5798</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9401</t>
+          <t>9497</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>178484</t>
+          <t>177646</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>187382</t>
+          <t>187492</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>196894</t>
+          <t>196606</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>207864</t>
+          <t>207654</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>378274</t>
+          <t>379519</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>392723</t>
+          <t>393541</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,97%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>3910</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12918</t>
+          <t>13756</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6585</t>
+          <t>6795</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17555</t>
+          <t>17843</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13128</t>
+          <t>12310</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>27577</t>
+          <t>26332</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>132040</t>
+          <t>131764</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>128810</t>
+          <t>129672</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>264490</t>
+          <t>264257</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>270779</t>
+          <t>270554</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5615</t>
+          <t>5891</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5004</t>
+          <t>4142</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>915</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6979</t>
+          <t>7212</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -5083,7 +5083,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>47130</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>65494</t>
+          <t>65782</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>115477</t>
+          <t>115271</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>121354</t>
+          <t>120907</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5290</t>
+          <t>5530</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6561</t>
+          <t>6767</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>590812</t>
+          <t>590417</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>608761</t>
+          <t>609532</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>630764</t>
+          <t>630265</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>650389</t>
+          <t>649893</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1227346</t>
+          <t>1227208</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1254932</t>
+          <t>1254761</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,68%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>26388</t>
+          <t>25617</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>44337</t>
+          <t>44732</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>25852</t>
+          <t>26348</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>45477</t>
+          <t>45976</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>56458</t>
+          <t>56629</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>84044</t>
+          <t>84182</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>62075</t>
+          <t>63154</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71731</t>
+          <t>72195</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>72271</t>
+          <t>72036</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>83523</t>
+          <t>82952</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>139190</t>
+          <t>138431</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>153242</t>
+          <t>152280</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>90,52%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5012</t>
+          <t>4548</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14668</t>
+          <t>13589</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7971</t>
+          <t>8542</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19223</t>
+          <t>19458</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14994</t>
+          <t>15956</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29046</t>
+          <t>29805</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,72%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77780</t>
+          <t>77516</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>88510</t>
+          <t>88400</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>80880</t>
+          <t>80508</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>90802</t>
+          <t>90821</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>162327</t>
+          <t>162289</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>176353</t>
+          <t>177372</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>91,02%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8423</t>
+          <t>8533</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19153</t>
+          <t>19417</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7145</t>
+          <t>7126</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17067</t>
+          <t>17439</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18527</t>
+          <t>17508</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>32553</t>
+          <t>32591</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,72%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48012</t>
+          <t>48343</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53620</t>
+          <t>53645</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>57810</t>
+          <t>57801</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64654</t>
+          <t>64561</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>108683</t>
+          <t>108223</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>117545</t>
+          <t>117208</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,19%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6768</t>
+          <t>6437</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2414</t>
+          <t>2507</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9258</t>
+          <t>9267</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>4640</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13165</t>
+          <t>13625</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,18%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>192473</t>
+          <t>192142</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>202041</t>
+          <t>201641</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>179535</t>
+          <t>179315</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>187051</t>
+          <t>187022</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>374917</t>
+          <t>374987</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>387642</t>
+          <t>387331</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,74%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5237</t>
+          <t>5637</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14805</t>
+          <t>15136</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9480</t>
+          <t>9700</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8650</t>
+          <t>8961</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>21375</t>
+          <t>21305</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>120228</t>
+          <t>120006</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>123046</t>
+          <t>123079</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>245365</t>
+          <t>245817</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>252032</t>
+          <t>252127</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -7493,7 +7493,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3981</t>
+          <t>4203</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7508,7 +7508,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5957</t>
+          <t>5924</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7847</t>
+          <t>7395</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>50983</t>
+          <t>50651</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>55714</t>
+          <t>55718</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -7753,7 +7753,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>57725</t>
+          <t>57307</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -7768,7 +7768,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>111568</t>
+          <t>110957</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>117220</t>
+          <t>117151</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>590</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5325</t>
+          <t>5657</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7871,7 +7871,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3880</t>
+          <t>4298</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>762</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6345</t>
+          <t>6956</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>567654</t>
+          <t>568665</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>586810</t>
+          <t>587059</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>588474</t>
+          <t>588046</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>607319</t>
+          <t>607324</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,7 +8111,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1163134</t>
+          <t>1163832</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1189979</t>
+          <t>1190497</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,06%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>29440</t>
+          <t>29191</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>48596</t>
+          <t>47585</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>28813</t>
+          <t>28808</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>47658</t>
+          <t>48086</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>62403</t>
+          <t>61885</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>89248</t>
+          <t>88550</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9786</t>
+          <t>9522</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>20329</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,7 +8673,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15977</t>
+          <t>15908</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27105</t>
+          <t>27444</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39735</t>
+          <t>40068</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>88,43%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4625</t>
+          <t>4444</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14987</t>
+          <t>15251</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4561</t>
+          <t>4630</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5576</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18206</t>
+          <t>17867</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>39,43%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2949</t>
+          <t>2762</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8377</t>
+          <t>8336</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9565</t>
+          <t>9601</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15428</t>
+          <t>15357</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14363</t>
+          <t>14712</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22666</t>
+          <t>22327</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>83,66%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>2155</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7542</t>
+          <t>7729</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>839</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6631</t>
+          <t>6595</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4021</t>
+          <t>4360</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12324</t>
+          <t>11975</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>44,87%</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7641</t>
+          <t>7075</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11015</t>
+          <t>10962</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -9409,7 +9409,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -9477,7 +9477,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3285</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9512,7 +9512,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3326</t>
+          <t>3379</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9527,7 +9527,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,56%</t>
         </is>
       </c>
     </row>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25595</t>
+          <t>26034</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -9682,7 +9682,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35034</t>
+          <t>34912</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40580</t>
+          <t>40508</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>63421</t>
+          <t>62958</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>69853</t>
+          <t>69779</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,82%</t>
         </is>
       </c>
     </row>
@@ -9785,7 +9785,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4607</t>
+          <t>4168</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>622</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6096</t>
+          <t>6218</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>1553</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7911</t>
+          <t>8374</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,74%</t>
         </is>
       </c>
     </row>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17016</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -10025,7 +10025,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -10080,7 +10080,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>47122</t>
+          <t>46922</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -10128,7 +10128,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3426</t>
+          <t>3560</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10198,7 +10198,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>3421</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -10353,7 +10353,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6540</t>
+          <t>6388</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8556</t>
+          <t>7761</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -10403,7 +10403,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -10423,7 +10423,7 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16788</t>
+          <t>16648</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -10471,7 +10471,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2816</t>
+          <t>2968</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10506,7 +10506,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3115</t>
+          <t>3910</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10521,7 +10521,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4240</t>
+          <t>4380</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,83%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>72594</t>
+          <t>72694</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>87739</t>
+          <t>88567</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>116158</t>
+          <t>115547</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>126177</t>
+          <t>125836</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>194508</t>
+          <t>192837</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>212288</t>
+          <t>212011</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,56%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10940</t>
+          <t>10112</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26085</t>
+          <t>25985</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4185</t>
+          <t>4526</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>14204</t>
+          <t>14815</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>17031</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>34534</t>
+          <t>36205</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,81%</t>
         </is>
       </c>
     </row>
